--- a/data/fixtures/metadata/ta_classifications.xlsx
+++ b/data/fixtures/metadata/ta_classifications.xlsx
@@ -566,7 +566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -580,6 +580,11 @@
           <t>description</t>
         </is>
       </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>gdp_component</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -592,6 +597,11 @@
           <t>Output at basic prices</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>output</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -604,6 +614,11 @@
           <t>Imports</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>imports</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -616,6 +631,11 @@
           <t>Intermediate consumption</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>intermediate</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -628,6 +648,11 @@
           <t>Household consumption</t>
         </is>
       </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>private_consumption</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -640,6 +665,11 @@
           <t>Government collective consumption</t>
         </is>
       </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>government_consumption</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -652,6 +682,11 @@
           <t>Gross fixed capital formation - dwellings</t>
         </is>
       </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>investment</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -662,6 +697,11 @@
       <c r="B8" t="inlineStr">
         <is>
           <t>Exports of domestic production</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>exports</t>
         </is>
       </c>
     </row>

--- a/data/fixtures/metadata/ta_classifications.xlsx
+++ b/data/fixtures/metadata/ta_classifications.xlsx
@@ -515,7 +515,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>name</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>name</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>name</t>
         </is>
       </c>
     </row>
@@ -815,7 +815,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>name</t>
         </is>
       </c>
     </row>

--- a/data/fixtures/metadata/ta_classifications.xlsx
+++ b/data/fixtures/metadata/ta_classifications.xlsx
@@ -566,7 +566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -580,11 +580,6 @@
           <t>name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>gdp_component</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -597,11 +592,6 @@
           <t>Output at basic prices</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>output</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -614,11 +604,6 @@
           <t>Imports</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>imports</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -631,11 +616,6 @@
           <t>Intermediate consumption</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>intermediate</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -648,11 +628,6 @@
           <t>Household consumption</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>private_consumption</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -665,11 +640,6 @@
           <t>Government collective consumption</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>government_consumption</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -682,11 +652,6 @@
           <t>Gross fixed capital formation - dwellings</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>investment</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -697,11 +662,6 @@
       <c r="B8" t="inlineStr">
         <is>
           <t>Exports of domestic production</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>exports</t>
         </is>
       </c>
     </row>

--- a/data/fixtures/metadata/ta_classifications.xlsx
+++ b/data/fixtures/metadata/ta_classifications.xlsx
@@ -566,7 +566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -580,6 +580,11 @@
           <t>name</t>
         </is>
       </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -592,6 +597,11 @@
           <t>Output at basic prices</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>supply</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -604,6 +614,11 @@
           <t>Imports</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>supply</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -616,6 +631,11 @@
           <t>Intermediate consumption</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>use</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -628,6 +648,11 @@
           <t>Household consumption</t>
         </is>
       </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>use</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -640,6 +665,11 @@
           <t>Government collective consumption</t>
         </is>
       </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>use</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -652,6 +682,11 @@
           <t>Gross fixed capital formation - dwellings</t>
         </is>
       </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>use</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -662,6 +697,11 @@
       <c r="B8" t="inlineStr">
         <is>
           <t>Exports of domestic production</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>use</t>
         </is>
       </c>
     </row>

--- a/data/fixtures/metadata/ta_classifications.xlsx
+++ b/data/fixtures/metadata/ta_classifications.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -552,6 +552,18 @@
       <c r="B4" t="inlineStr">
         <is>
           <t>Product C</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Trade services</t>
         </is>
       </c>
     </row>
@@ -566,7 +578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -674,12 +686,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5110</t>
+          <t>5139</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Gross fixed capital formation - dwellings</t>
+          <t>Gross fixed capital formation - other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -691,15 +703,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>5200</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Changes in inventories</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>use</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>6001</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Exports of domestic production</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>use</t>
         </is>
@@ -716,7 +745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -752,6 +781,18 @@
       <c r="B3" t="inlineStr">
         <is>
           <t>Industry Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Trade industry</t>
         </is>
       </c>
     </row>
@@ -789,7 +830,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Household</t>
+          <t>Households</t>
         </is>
       </c>
     </row>

--- a/data/fixtures/metadata/ta_classifications.xlsx
+++ b/data/fixtures/metadata/ta_classifications.xlsx
@@ -578,7 +578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -597,6 +597,11 @@
           <t>table</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>esa_code</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -614,6 +619,11 @@
           <t>supply</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -631,6 +641,11 @@
           <t>supply</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -648,6 +663,11 @@
           <t>use</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -665,6 +685,11 @@
           <t>use</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>P31</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -682,6 +707,11 @@
           <t>use</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>P32</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -699,6 +729,11 @@
           <t>use</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>P51g</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -716,6 +751,11 @@
           <t>use</t>
         </is>
       </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>P52</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -731,6 +771,11 @@
       <c r="C9" t="inlineStr">
         <is>
           <t>use</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>P6</t>
         </is>
       </c>
     </row>

--- a/data/fixtures/metadata/ta_classifications.xlsx
+++ b/data/fixtures/metadata/ta_classifications.xlsx
@@ -510,12 +510,12 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>code</t>
+          <t>nrnr</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>nrnr_txt</t>
         </is>
       </c>
     </row>
@@ -584,12 +584,12 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>code</t>
+          <t>trans</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>trans_txt</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -796,12 +796,12 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>code</t>
+          <t>brch</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>brch_txt</t>
         </is>
       </c>
     </row>
@@ -858,12 +858,12 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>code</t>
+          <t>brch</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>brch_txt</t>
         </is>
       </c>
     </row>
@@ -896,12 +896,12 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>code</t>
+          <t>brch</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>brch_txt</t>
         </is>
       </c>
     </row>
